--- a/Accounting_Audit/xlsx_file/depreciation_amortization_line.xlsx
+++ b/Accounting_Audit/xlsx_file/depreciation_amortization_line.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/未命名/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lei/Downloads/Python_SQL_PowerBI_Excel/Accounting_Audit/xlsx_file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9365AA-FCDC-6B47-8A6A-EC41C06555ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F172EC-DCD9-2E48-9B8C-285276CCABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="660" windowWidth="28480" windowHeight="16080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet" sheetId="1" r:id="rId2"/>
+    <sheet name="测算表" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,30 @@
   <si>
     <r>
       <rPr>
-        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上年末资产负债表日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>资产负债表日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -50,7 +73,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -62,7 +84,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -74,7 +95,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -86,7 +106,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -98,7 +117,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -110,7 +128,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -122,7 +139,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -134,7 +150,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -144,7 +159,6 @@
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
@@ -153,7 +167,6 @@
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -165,7 +178,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -177,7 +189,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -189,7 +200,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -201,7 +211,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -213,7 +222,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -225,7 +233,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -237,7 +244,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -249,7 +255,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -261,7 +266,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -273,37 +277,12 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>差额</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>上年末资产负债表日</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>资产负债表日</t>
     </r>
   </si>
 </sst>
@@ -312,8 +291,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="[$-409]yyyy/mm/dd;@"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="[$-409]yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -327,6 +306,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -338,19 +318,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -359,6 +326,17 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -378,7 +356,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -401,21 +379,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -425,56 +388,53 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -961,24 +921,24 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="7" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="16">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10">
         <v>45657</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="16">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10">
         <v>46022</v>
       </c>
     </row>
@@ -993,115 +953,115 @@
   <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="10.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="8" customWidth="1"/>
-    <col min="4" max="5" width="10.6640625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" style="10" customWidth="1"/>
-    <col min="8" max="9" width="15.6640625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="12" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" style="13" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" style="9" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" style="13" customWidth="1"/>
-    <col min="14" max="14" width="15.6640625" style="9" customWidth="1"/>
-    <col min="15" max="15" width="15.6640625" style="13" customWidth="1"/>
-    <col min="16" max="19" width="15.6640625" style="9" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="7"/>
+    <col min="1" max="2" width="10.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="10.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" style="4" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" style="7" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" style="7" customWidth="1"/>
+    <col min="16" max="19" width="15.6640625" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="16" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="D1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="F1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="G1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="H1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="I1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="J1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="K1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="L1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="M1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="N1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="O1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="P1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="Q1" s="13" t="s">
         <v>18</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="13" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="16" customHeight="1">
-      <c r="H2" s="11">
+      <c r="H2" s="5">
         <f>F2*G2</f>
         <v>0</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="5">
         <f>F2-H2</f>
         <v>0</v>
       </c>
-      <c r="L2" s="11" t="e">
+      <c r="L2" s="5" t="e">
         <f>I2/K2*(IF(DATEDIF(J2,info!$B$1,"M")&gt;K2,K2,IF(DATEDIF(J2,info!$B$1,"M")&gt;0,DATEDIF(J2,info!$B$1,"M"),0)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="8">
         <f>IF(AND(DATEDIF(J2,info!$B$2,"M")&lt;13,DATEDIF(J2,info!$B$2,"M")&gt;0),DATEDIF(J2,info!$B$2,"M"),IF(K2-DATEDIF(J2,info!$B$1,"M")&gt;12,12,IF(K2-DATEDIF(J2,info!$B$1,"M")&lt;0,0,K2-DATEDIF(J2,info!$B$1,"M"))))</f>
         <v>0</v>
       </c>
-      <c r="N2" s="11" t="e">
+      <c r="N2" s="5" t="e">
         <f>I2/K2*M2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O2" s="14">
+      <c r="O2" s="8">
         <f>IF(DATEDIF(J2,info!$B$2,"M")&gt;K2,K2,DATEDIF(J2,info!$B$2,"M"))</f>
         <v>0</v>
       </c>
-      <c r="P2" s="11" t="e">
+      <c r="P2" s="5" t="e">
         <f>L2+N2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q2" s="11" t="e">
+      <c r="Q2" s="5" t="e">
         <f>F2-P2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S2" s="11" t="e">
+      <c r="S2" s="5" t="e">
         <f>Q2-R2</f>
         <v>#DIV/0!</v>
       </c>
